--- a/outputs/2025/09setembro/tabelas_relatorio_2025-09.xlsx
+++ b/outputs/2025/09setembro/tabelas_relatorio_2025-09.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://judfunpresp-my.sharepoint.com/personal/giovana_silva_funprespjud_com_br/Documents/Imagens/relatorio-gerencial-auto/outputs/2025/09setembro/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_79267D4406BB1BFF06C8D187AAB46BD5E9BD6D16" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C324A37-AE1C-4EB6-AC55-8921FB4B0F11}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_79267D4406BB1BFF06C8D187AAB46BD5E9BD6D16" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{977E3E2E-EF27-4424-9294-1A4B69CFEE28}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1 - Evolução Adesões" sheetId="1" r:id="rId1"/>
